--- a/balance_tables/普通强化.xlsx
+++ b/balance_tables/普通强化.xlsx
@@ -1179,7 +1179,7 @@
         <v>0.05</v>
       </c>
       <c r="E2" s="19" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="D3" s="20" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D5" s="20" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D6" s="20" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="30" customWidth="1" style="39" min="1" max="1"/>
@@ -1991,11 +1991,101 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>结构版本，请勿修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>reward_effect_scale</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>食客小份奖励的效果、额外胃口与升值血量缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wine_curve_c</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>结构版本，请勿修改</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>酒的对数软化参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>range_curve_c</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>葱的对数软化参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>duration_curve_c</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>淀粉的对数软化参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cart_speed_curve_c</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>轻便餐车的对数软化参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>range_multiplier_cap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17.6470588235</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>土豆判定直径覆盖六区的异常保护倍率</t>
         </is>
       </c>
     </row>

--- a/balance_tables/普通强化.xlsx
+++ b/balance_tables/普通强化.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46D7A69-203F-4A1C-837A-7CA066B8FDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D57AB5B-EAA8-4E7C-90F9-F5590362E5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通强化预览" sheetId="1" r:id="rId1"/>
@@ -1121,19 +1121,19 @@
       </c>
       <c r="D10" s="28">
         <f t="shared" si="0"/>
-        <v>4.2499999999999996E-2</v>
+        <v>0.09</v>
       </c>
       <c r="E10" s="28">
         <f t="shared" si="1"/>
-        <v>6.5000000000000002E-2</v>
+        <v>0.15999999999999998</v>
       </c>
       <c r="F10" s="28">
         <f t="shared" si="2"/>
-        <v>8.7500000000000008E-2</v>
+        <v>0.22999999999999995</v>
       </c>
       <c r="G10" s="28">
         <f>普通门!E5</f>
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="5" t="str">
         <f>普通门!F5</f>
@@ -1159,23 +1159,23 @@
       </c>
       <c r="C11" s="27">
         <f>普通门!D6</f>
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="D11" s="27">
         <f t="shared" si="0"/>
-        <v>0.22750000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="E11" s="27">
         <f t="shared" si="1"/>
-        <v>0.33500000000000002</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F11" s="27">
         <f t="shared" si="2"/>
-        <v>0.4425</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="G11" s="27">
         <f>普通门!E6</f>
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="5" t="str">
         <f>普通门!F6</f>
@@ -1467,7 +1467,7 @@
         <v>0.02</v>
       </c>
       <c r="E5" s="20">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>20</v>
@@ -1490,10 +1490,10 @@
         <v>32</v>
       </c>
       <c r="D6" s="20">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E6" s="20">
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>20</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="E15" s="37">
         <f>普通门!E5</f>
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="F15" s="36" t="str">
         <f>普通门!F5</f>
@@ -1917,11 +1917,11 @@
       </c>
       <c r="D16" s="35">
         <f>普通门!D6</f>
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E16" s="35">
         <f>普通门!E6</f>
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="36" t="str">
         <f>普通门!F6</f>
